--- a/python-excel-k-means-demo.xlsx
+++ b/python-excel-k-means-demo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2000001_{3046EC21-9349-4DFF-8C26-F5AF99169A00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0FCF7-779A-4F03-92C2-71A8BB06FCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -801,9 +801,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="\$#,##0"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -858,7 +859,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -867,6 +868,7 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -894,8 +896,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>313267</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>21167</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>1482</xdr:rowOff>
     </xdr:to>
@@ -943,8 +945,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>385582</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>576082</xdr:colOff>
       <xdr:row>69</xdr:row>
       <xdr:rowOff>150207</xdr:rowOff>
     </xdr:to>
@@ -1580,6 +1582,13 @@
     <col min="9" max="9" width="12.6640625" customWidth="1"/>
     <col min="10" max="10" width="18.1640625" customWidth="1"/>
     <col min="12" max="12" width="9.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.71875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18">
@@ -1781,26 +1790,26 @@
       <c r="J6">
         <v>6</v>
       </c>
-      <c r="L6" cm="1">
+      <c r="L6" s="6" cm="1">
         <f t="array" ref="L6:R10">_xlfn._xlws.PY(2,0)</f>
         <v>-1.3041373356770676</v>
       </c>
-      <c r="M6">
+      <c r="M6" s="6">
         <v>-1.1759853469283887</v>
       </c>
-      <c r="N6">
+      <c r="N6" s="6">
         <v>-0.2910777741683534</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="6">
         <v>0.22421989408751555</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="6">
         <v>1.2613947726042967</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="6">
         <v>1.3983257229103461</v>
       </c>
-      <c r="R6">
+      <c r="R6" s="6">
         <v>0.64669672942704892</v>
       </c>
     </row>
@@ -1835,25 +1844,25 @@
       <c r="J7">
         <v>46</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="6">
         <v>-1.3103817555250041</v>
       </c>
-      <c r="M7">
+      <c r="M7" s="6">
         <v>-1.1013722477224988</v>
       </c>
-      <c r="N7">
+      <c r="N7" s="6">
         <v>-0.50836383045830491</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="6">
         <v>0.4772997745427317</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="6">
         <v>-7.419969250613502E-2</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="6">
         <v>3.0542377631989139</v>
       </c>
-      <c r="R7">
+      <c r="R7" s="6">
         <v>0.94478997218471561</v>
       </c>
     </row>
@@ -1888,25 +1897,25 @@
       <c r="J8">
         <v>31</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="6">
         <v>-0.33592805686202654</v>
       </c>
-      <c r="M8">
+      <c r="M8" s="6">
         <v>1.3608600260718715</v>
       </c>
-      <c r="N8">
+      <c r="N8" s="6">
         <v>-1.1145362131338621</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="6">
         <v>1.4762993026554263</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="6">
         <v>-0.12556871039499784</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="6">
         <v>-0.25758631737822169</v>
       </c>
-      <c r="R8">
+      <c r="R8" s="6">
         <v>-0.67609203531009676</v>
       </c>
     </row>
@@ -1941,25 +1950,25 @@
       <c r="J9">
         <v>14</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="6">
         <v>0.21257304321208076</v>
       </c>
-      <c r="M9">
+      <c r="M9" s="6">
         <v>1.8831517205131016</v>
       </c>
-      <c r="N9">
+      <c r="N9" s="6">
         <v>-0.82563186229985663</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="6">
         <v>1.3297793718655642</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="6">
         <v>2.8538343271588473E-3</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="6">
         <v>-1.0855423375225055</v>
       </c>
-      <c r="R9">
+      <c r="R9" s="6">
         <v>-0.86240031203363843</v>
       </c>
     </row>
@@ -1994,25 +2003,25 @@
       <c r="J10">
         <v>28</v>
       </c>
-      <c r="L10">
+      <c r="L10" s="6">
         <v>1.4992195427601547</v>
       </c>
-      <c r="M10">
+      <c r="M10" s="6">
         <v>0.83856833163064148</v>
       </c>
-      <c r="N10">
+      <c r="N10" s="6">
         <v>3.6006117279025239E-3</v>
       </c>
-      <c r="O10">
+      <c r="O10" s="6">
         <v>-1.1876994389784257</v>
       </c>
-      <c r="P10">
+      <c r="P10" s="6">
         <v>-1.7180082649497437</v>
       </c>
-      <c r="Q10">
+      <c r="Q10" s="6">
         <v>-0.25758631737822169</v>
       </c>
-      <c r="R10">
+      <c r="R10" s="6">
         <v>-1.1232318994465966</v>
       </c>
     </row>

--- a/python-excel-k-means-demo.xlsx
+++ b/python-excel-k-means-demo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\georg\Documents\GitHub\blog-files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83C0FCF7-779A-4F03-92C2-71A8BB06FCAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24AAF449-2B74-4B91-A3BB-0D004CA50A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="16826" windowHeight="11280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -48,7 +48,7 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="4">
+  <futureMetadata name="XLRICHVALUE" count="5">
     <bk>
       <extLst>
         <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
@@ -77,13 +77,20 @@
         </ext>
       </extLst>
     </bk>
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="8"/>
+        </ext>
+      </extLst>
+    </bk>
   </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="4">
+  <valueMetadata count="5">
     <bk>
       <rc t="2" v="0"/>
     </bk>
@@ -96,6 +103,9 @@
     <bk>
       <rc t="2" v="3"/>
     </bk>
+    <bk>
+      <rc t="2" v="4"/>
+    </bk>
   </valueMetadata>
 </metadata>
 </file>
@@ -103,7 +113,7 @@
 <file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
 <python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
   <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
-    <initialization>
+    <initialization userModified="1">
       <code xml:space="preserve">import numpy as np
 import pandas as pd
 import matplotlib.pyplot as plt
@@ -1267,7 +1277,7 @@
 </file>
 
 <file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="8">
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="9">
   <rv s="0">
     <v>0</v>
   </rv>
@@ -1305,11 +1315,14 @@
     <v>2</v>
   </rv>
   <rv s="3">
+    <v>14</v>
+  </rv>
+  <rv s="4">
     <v>0</v>
     <v>9</v>
     <v>Image generated by Python</v>
   </rv>
-  <rv s="3">
+  <rv s="4">
     <v>1</v>
     <v>9</v>
     <v>Image generated by Python</v>
@@ -1318,7 +1331,7 @@
 </file>
 
 <file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="4">
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="5">
   <s t="_array">
     <k n="array" t="a"/>
   </s>
@@ -1333,6 +1346,9 @@
     <k n="Python_str" t="s"/>
     <k n="preview" t="r"/>
     <k n="_Provider" t="spb"/>
+  </s>
+  <s t="_error">
+    <k n="errorType" t="i"/>
   </s>
   <s t="_localImage">
     <k n="_rvRel:LocalImageIdentifier" t="i"/>
@@ -1568,7 +1584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S181"/>
+  <dimension ref="A1:R181"/>
   <sheetFormatPr defaultRowHeight="13.7"/>
   <cols>
     <col min="1" max="1" width="10.109375" customWidth="1"/>
@@ -1623,7 +1639,7 @@
         <v>9</v>
       </c>
       <c r="L1" t="e" cm="1" vm="1">
-        <f t="array" ref="L1">_xlfn._xlws.PY(0,1,CustomerData[#All])</f>
+        <f t="array" aca="1" ref="L1" ca="1">_xlfn._xlws.PY(0,1,CustomerData[#All])</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1723,7 +1739,7 @@
         <v>30</v>
       </c>
       <c r="L4" t="e" cm="1" vm="2">
-        <f t="array" ref="L4">_xlfn._xlws.PY(1,1)</f>
+        <f t="array" aca="1" ref="L4" ca="1">_xlfn._xlws.PY(1,1)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -1791,25 +1807,31 @@
         <v>6</v>
       </c>
       <c r="L6" s="6" cm="1">
-        <f t="array" ref="L6:R10">_xlfn._xlws.PY(2,0)</f>
+        <f t="array" aca="1" ref="L6:R10" ca="1">_xlfn._xlws.PY(2,0)</f>
         <v>-1.3041373356770676</v>
       </c>
       <c r="M6" s="6">
+        <f ca="1"/>
         <v>-1.1759853469283887</v>
       </c>
       <c r="N6" s="6">
+        <f ca="1"/>
         <v>-0.2910777741683534</v>
       </c>
       <c r="O6" s="6">
+        <f ca="1"/>
         <v>0.22421989408751555</v>
       </c>
       <c r="P6" s="6">
+        <f ca="1"/>
         <v>1.2613947726042967</v>
       </c>
       <c r="Q6" s="6">
+        <f ca="1"/>
         <v>1.3983257229103461</v>
       </c>
       <c r="R6" s="6">
+        <f ca="1"/>
         <v>0.64669672942704892</v>
       </c>
     </row>
@@ -1845,24 +1867,31 @@
         <v>46</v>
       </c>
       <c r="L7" s="6">
+        <f ca="1"/>
         <v>-1.3103817555250041</v>
       </c>
       <c r="M7" s="6">
+        <f ca="1"/>
         <v>-1.1013722477224988</v>
       </c>
       <c r="N7" s="6">
+        <f ca="1"/>
         <v>-0.50836383045830491</v>
       </c>
       <c r="O7" s="6">
+        <f ca="1"/>
         <v>0.4772997745427317</v>
       </c>
       <c r="P7" s="6">
+        <f ca="1"/>
         <v>-7.419969250613502E-2</v>
       </c>
       <c r="Q7" s="6">
+        <f ca="1"/>
         <v>3.0542377631989139</v>
       </c>
       <c r="R7" s="6">
+        <f ca="1"/>
         <v>0.94478997218471561</v>
       </c>
     </row>
@@ -1898,24 +1927,31 @@
         <v>31</v>
       </c>
       <c r="L8" s="6">
+        <f ca="1"/>
         <v>-0.33592805686202654</v>
       </c>
       <c r="M8" s="6">
+        <f ca="1"/>
         <v>1.3608600260718715</v>
       </c>
       <c r="N8" s="6">
+        <f ca="1"/>
         <v>-1.1145362131338621</v>
       </c>
       <c r="O8" s="6">
+        <f ca="1"/>
         <v>1.4762993026554263</v>
       </c>
       <c r="P8" s="6">
+        <f ca="1"/>
         <v>-0.12556871039499784</v>
       </c>
       <c r="Q8" s="6">
+        <f ca="1"/>
         <v>-0.25758631737822169</v>
       </c>
       <c r="R8" s="6">
+        <f ca="1"/>
         <v>-0.67609203531009676</v>
       </c>
     </row>
@@ -1951,24 +1987,31 @@
         <v>14</v>
       </c>
       <c r="L9" s="6">
+        <f ca="1"/>
         <v>0.21257304321208076</v>
       </c>
       <c r="M9" s="6">
+        <f ca="1"/>
         <v>1.8831517205131016</v>
       </c>
       <c r="N9" s="6">
+        <f ca="1"/>
         <v>-0.82563186229985663</v>
       </c>
       <c r="O9" s="6">
+        <f ca="1"/>
         <v>1.3297793718655642</v>
       </c>
       <c r="P9" s="6">
+        <f ca="1"/>
         <v>2.8538343271588473E-3</v>
       </c>
       <c r="Q9" s="6">
+        <f ca="1"/>
         <v>-1.0855423375225055</v>
       </c>
       <c r="R9" s="6">
+        <f ca="1"/>
         <v>-0.86240031203363843</v>
       </c>
     </row>
@@ -2004,24 +2047,31 @@
         <v>28</v>
       </c>
       <c r="L10" s="6">
+        <f ca="1"/>
         <v>1.4992195427601547</v>
       </c>
       <c r="M10" s="6">
+        <f ca="1"/>
         <v>0.83856833163064148</v>
       </c>
       <c r="N10" s="6">
+        <f ca="1"/>
         <v>3.6006117279025239E-3</v>
       </c>
       <c r="O10" s="6">
+        <f ca="1"/>
         <v>-1.1876994389784257</v>
       </c>
       <c r="P10" s="6">
+        <f ca="1"/>
         <v>-1.7180082649497437</v>
       </c>
       <c r="Q10" s="6">
+        <f ca="1"/>
         <v>-0.25758631737822169</v>
       </c>
       <c r="R10" s="6">
+        <f ca="1"/>
         <v>-1.1232318994465966</v>
       </c>
     </row>
@@ -2088,8 +2138,8 @@
       <c r="J12">
         <v>38</v>
       </c>
-      <c r="L12" t="e" cm="1" vm="3">
-        <f t="array" ref="L12">_xlfn._xlws.PY(3,0)</f>
+      <c r="L12" t="e" cm="1" vm="4">
+        <f t="array" aca="1" ref="L12" ca="1">_xlfn._xlws.PY(3,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
@@ -2733,11 +2783,11 @@
         <v>36</v>
       </c>
       <c r="L32" t="str" cm="1">
-        <f t="array" ref="L32:L37">_xlfn._xlws.PY(4,0)</f>
+        <f t="array" aca="1" ref="L32:L37" ca="1">_xlfn._xlws.PY(4,0)</f>
         <v>cluster</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:12">
       <c r="A33" t="s">
         <v>49</v>
       </c>
@@ -2769,10 +2819,11 @@
         <v>38</v>
       </c>
       <c r="L33">
+        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
         <v>50</v>
       </c>
@@ -2804,10 +2855,11 @@
         <v>283</v>
       </c>
       <c r="L34">
+        <f ca="1"/>
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:12">
       <c r="A35" t="s">
         <v>51</v>
       </c>
@@ -2839,10 +2891,11 @@
         <v>65</v>
       </c>
       <c r="L35">
+        <f ca="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:12">
       <c r="A36" t="s">
         <v>52</v>
       </c>
@@ -2874,10 +2927,11 @@
         <v>22</v>
       </c>
       <c r="L36">
+        <f ca="1"/>
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:12">
       <c r="A37" t="s">
         <v>53</v>
       </c>
@@ -2909,10 +2963,11 @@
         <v>160</v>
       </c>
       <c r="L37">
+        <f ca="1"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:12">
       <c r="A38" t="s">
         <v>54</v>
       </c>
@@ -2944,7 +2999,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:12">
       <c r="A39" t="s">
         <v>55</v>
       </c>
@@ -2975,33 +3030,12 @@
       <c r="J39">
         <v>91</v>
       </c>
-      <c r="L39" t="str" cm="1">
-        <f t="array" ref="L39:S44">_xlfn._xlws.PY(5,0)</f>
-        <v/>
-      </c>
-      <c r="M39" t="str">
-        <v>annual_spend</v>
-      </c>
-      <c r="N39" t="str">
-        <v>orders_per_year</v>
-      </c>
-      <c r="O39" t="str">
-        <v>avg_order_value</v>
-      </c>
-      <c r="P39" t="str">
-        <v>discount_rate</v>
-      </c>
-      <c r="Q39" t="str">
-        <v>returns_rate</v>
-      </c>
-      <c r="R39" t="str">
-        <v>support_tickets</v>
-      </c>
-      <c r="S39" t="str">
-        <v>days_since_last_order</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
+      <c r="L39" cm="1">
+        <f t="array" aca="1" ref="L39" ca="1">_xlfn._xlws.PY(5,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
         <v>56</v>
       </c>
@@ -3032,32 +3066,8 @@
       <c r="J40">
         <v>91</v>
       </c>
-      <c r="L40" t="str">
-        <v>cluster</v>
-      </c>
-      <c r="M40" t="str">
-        <v/>
-      </c>
-      <c r="N40" t="str">
-        <v/>
-      </c>
-      <c r="O40" t="str">
-        <v/>
-      </c>
-      <c r="P40" t="str">
-        <v/>
-      </c>
-      <c r="Q40" t="str">
-        <v/>
-      </c>
-      <c r="R40" t="str">
-        <v/>
-      </c>
-      <c r="S40" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+    </row>
+    <row r="41" spans="1:12">
       <c r="A41" t="s">
         <v>57</v>
       </c>
@@ -3088,32 +3098,8 @@
       <c r="J41">
         <v>36</v>
       </c>
-      <c r="L41">
-        <v>0</v>
-      </c>
-      <c r="M41">
-        <v>4246.88</v>
-      </c>
-      <c r="N41">
-        <v>27.02</v>
-      </c>
-      <c r="O41">
-        <v>153.38</v>
-      </c>
-      <c r="P41">
-        <v>0.08</v>
-      </c>
-      <c r="Q41">
-        <v>0.03</v>
-      </c>
-      <c r="R41">
-        <v>0.73</v>
-      </c>
-      <c r="S41">
-        <v>23.67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+    </row>
+    <row r="42" spans="1:12">
       <c r="A42" t="s">
         <v>58</v>
       </c>
@@ -3144,32 +3130,8 @@
       <c r="J42">
         <v>83</v>
       </c>
-      <c r="L42">
-        <v>1</v>
-      </c>
-      <c r="M42">
-        <v>553.53</v>
-      </c>
-      <c r="N42">
-        <v>3.31</v>
-      </c>
-      <c r="O42">
-        <v>149.35</v>
-      </c>
-      <c r="P42">
-        <v>0.18</v>
-      </c>
-      <c r="Q42">
-        <v>0.12</v>
-      </c>
-      <c r="R42">
-        <v>2.72</v>
-      </c>
-      <c r="S42">
-        <v>150.13</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19">
+    </row>
+    <row r="43" spans="1:12">
       <c r="A43" t="s">
         <v>59</v>
       </c>
@@ -3200,32 +3162,8 @@
       <c r="J43">
         <v>19</v>
       </c>
-      <c r="L43">
-        <v>2</v>
-      </c>
-      <c r="M43">
-        <v>2207.59</v>
-      </c>
-      <c r="N43">
-        <v>31.44</v>
-      </c>
-      <c r="O43">
-        <v>71.86</v>
-      </c>
-      <c r="P43">
-        <v>0.24</v>
-      </c>
-      <c r="Q43">
-        <v>0.08</v>
-      </c>
-      <c r="R43">
-        <v>1.33</v>
-      </c>
-      <c r="S43">
-        <v>35.6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
+    </row>
+    <row r="44" spans="1:12">
       <c r="A44" t="s">
         <v>60</v>
       </c>
@@ -3256,32 +3194,8 @@
       <c r="J44">
         <v>98</v>
       </c>
-      <c r="L44">
-        <v>3</v>
-      </c>
-      <c r="M44">
-        <v>2441.38</v>
-      </c>
-      <c r="N44">
-        <v>7.39</v>
-      </c>
-      <c r="O44">
-        <v>324.63</v>
-      </c>
-      <c r="P44">
-        <v>0.1</v>
-      </c>
-      <c r="Q44">
-        <v>0.06</v>
-      </c>
-      <c r="R44">
-        <v>0.59</v>
-      </c>
-      <c r="S44">
-        <v>74.489999999999995</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19">
+    </row>
+    <row r="45" spans="1:12">
       <c r="A45" t="s">
         <v>61</v>
       </c>
@@ -3313,7 +3227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:12">
       <c r="A46" t="s">
         <v>62</v>
       </c>
@@ -3345,7 +3259,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:12">
       <c r="A47" t="s">
         <v>63</v>
       </c>
@@ -3376,12 +3290,12 @@
       <c r="J47">
         <v>76</v>
       </c>
-      <c r="L47" t="e" cm="1" vm="4">
-        <f t="array" ref="L47">_xlfn._xlws.PY(6,0)</f>
+      <c r="L47" t="e" cm="1" vm="5">
+        <f t="array" aca="1" ref="L47" ca="1">_xlfn._xlws.PY(6,0)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:12">
       <c r="A48" t="s">
         <v>64</v>
       </c>
